--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0ddbcc4ed27d4f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b283ca9d2a84328"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b283ca9d2a84328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80eb2f0855b44d53"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80eb2f0855b44d53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R81cf6fcd39c64bd3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R81cf6fcd39c64bd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdf5f02c31cfc4929"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdf5f02c31cfc4929"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2300bea02b724a15"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2300bea02b724a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6fd49735267f410e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6fd49735267f410e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcda4f9daebfa4ac4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcda4f9daebfa4ac4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8a7a335560654abb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8a7a335560654abb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R652b4b9875744329"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R652b4b9875744329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8635f0d9ca164985"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8635f0d9ca164985"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc0d14b4336654161"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc0d14b4336654161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R55d19c35b73a4ba8"/>
   </x:sheets>
 </x:workbook>
 </file>
